--- a/data.mn/public/datasets/gdp-by-sector.xlsx
+++ b/data.mn/public/datasets/gdp-by-sector.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="English" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Монгол" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -416,7 +417,7 @@
   <dimension ref="A1:B21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
@@ -635,4 +636,234 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>салбар</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>утга</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Хөдөө аж ахуй, ойн аж ахуй, загас барилт, ан агнуур</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>8039329.45</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Уул уурхай, олборлолт</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>22747077.61</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Боловсруулах үйлдвэрлэл</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>5284027.69</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Цахилгаан, хий, уур, агааржуулалт</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1550908.71</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Усан хангамж; бохир ус, хог, хаягдлын менежмент болон цэвэрлэх үйл ажиллагаа</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>469082.69</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Барилга</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>3450418.23</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Бөөний болон жижиглэн худалдаа, машин, мотоциклийн засвар, үйлчилгээ</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>8969213.130000001</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Тээвэр ба агуулахын үйл ажиллагаа</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>4276301.79</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Зочид буудал, байр, сууц болон нийтийн хоолны үйлчилгээ</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1072875.72</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Мэдээлэл, холбоо</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1826150.14</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Санхүүгийн болон даатгалын үйл ажиллагаа</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>5174552.61</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Үл хөдлөх хөрөнгийн үйл ажиллагаа</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>4230720.83</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Мэргэжлийн, шинжлэх ухаан болон техникийн үйл ажиллагаа</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1389266.05</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Удирдлагын болон дэмжлэг үзүүлэх үйл ажиллагаа</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>697285.24</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Төрийн удирдлага ба батлан хамгаалах үйл ажиллагаа, албан журмын нийгмийн хамгаалал</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>4778646.55</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Боловсрол</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>4428877.1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Хүний эрүүл мэнд ба нийгмийн үйл ажиллагаа</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>2161544.8</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Урлаг, үзвэр, тоглоом, наадам</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>485584.91</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Үйлчилгээний бусад үйл ажиллагаа</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>388404.33</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Бүтээгдэхүүний цэвэр татвар</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>8516860.050000001</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>